--- a/docs/workbooks/high-confidence-recovery.xlsx
+++ b/docs/workbooks/high-confidence-recovery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anil\GitHub\newbridge-saas-operating-system\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anil\GitHub\newbridge-saas-operating-system\docs\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F1A79C-034D-46F2-8B21-CA1B31923F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866164F9-1E57-4EE2-801F-955427154D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="0" windowWidth="20370" windowHeight="15480" activeTab="1" xr2:uid="{E93CEB74-9002-4B77-A4DA-58E626EA608A}"/>
+    <workbookView xWindow="4560" yWindow="30" windowWidth="20370" windowHeight="15480" activeTab="1" xr2:uid="{E93CEB74-9002-4B77-A4DA-58E626EA608A}"/>
   </bookViews>
   <sheets>
     <sheet name="LP-Scenario8" sheetId="1" r:id="rId1"/>
@@ -831,6 +831,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00,,&quot;M&quot;"/>
+  </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1012,7 +1015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1120,6 +1123,7 @@
     <xf numFmtId="3" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1164,7 +1168,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1177,20 +1181,20 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-GB" sz="1050" b="1">
+              <a:rPr lang="en-GB" sz="1050" b="0">
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:t>Total</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-GB" sz="1050" b="1" baseline="0">
+              <a:rPr lang="en-GB" sz="1050" b="0" baseline="0">
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:t> Forecast Lift vs. ROI</a:t>
             </a:r>
-            <a:endParaRPr lang="en-GB" sz="1050" b="1">
+            <a:endParaRPr lang="en-GB" sz="1050" b="0">
               <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
             </a:endParaRPr>
@@ -1210,7 +1214,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1339,9 +1343,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'LP-Scenario9A'!$B$61:$B$65</c:f>
+              <c:f>'LP-Scenario9A'!$E$70:$E$74</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>#,##0.00,,"M"</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>24447302.333333336</c:v>
@@ -1562,16 +1566,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1605,7 +1609,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0.00,,&quot;M&quot;" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1628,9 +1632,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1670,9 +1674,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1730,9 +1734,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2331,15 +2335,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>29765</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>21432</xdr:rowOff>
+      <xdr:colOff>135594</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>169599</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1202530</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>70110</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5899,26 +5903,41 @@
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E70" s="53">
+        <v>24447302.333333336</v>
+      </c>
       <c r="K70" s="34" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E71" s="53">
+        <v>28237120.979797978</v>
+      </c>
       <c r="K71" s="34" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E72" s="53">
+        <v>31770125.229437232</v>
+      </c>
       <c r="K72" s="34" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E73" s="53">
+        <v>33315579.774891771</v>
+      </c>
       <c r="K73" s="34" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E74" s="53">
+        <v>34760786</v>
+      </c>
       <c r="K74" s="34" t="s">
         <v>70</v>
       </c>
